--- a/VerveStacks_ESP_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ESP_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3144B9CC-9ED2-44E8-AB43-408AB8BE142F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7347DF93-1FA0-4395-8DBE-34EFA11C0B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2DA39F51-EA4B-4108-B191-649B8D7987E0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E38256AE-3828-44F8-B08C-91E1A1F7A1F3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2650,7 +2650,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4786E270-160B-46EB-81E9-A845EA96B7A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4773F964-297E-44CA-8AB0-7A5082679A62}">
   <dimension ref="B3:L344"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
